--- a/backend/src/tmp/cotizacionConcreto.xlsx
+++ b/backend/src/tmp/cotizacionConcreto.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="65">
   <si>
     <t xml:space="preserve">CLIENTE: </t>
   </si>
@@ -172,61 +172,52 @@
     <t>C.C. 25 -0003</t>
   </si>
   <si>
-    <t>Inversiones santa maria C.A</t>
-  </si>
-  <si>
-    <t>23568958</t>
-  </si>
-  <si>
-    <t>25-152</t>
-  </si>
-  <si>
-    <t>2025-11-19</t>
-  </si>
-  <si>
-    <t>04128569569</t>
-  </si>
-  <si>
-    <t>2 dias</t>
-  </si>
-  <si>
-    <t>Contado</t>
-  </si>
-  <si>
-    <t>muy lejos</t>
-  </si>
-  <si>
-    <t>Juan Gomez</t>
-  </si>
-  <si>
-    <t>0145-2512521</t>
+    <t>Albañiles Juan y Pedro C.A</t>
+  </si>
+  <si>
+    <t>8867149</t>
+  </si>
+  <si>
+    <t>26-001-C</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>04121234567</t>
+  </si>
+  <si>
+    <t>5 dias</t>
+  </si>
+  <si>
+    <t>efectivo</t>
+  </si>
+  <si>
+    <t>Puerto Ordaz</t>
+  </si>
+  <si>
+    <t>Joseph Martinez</t>
+  </si>
+  <si>
+    <t>04161235456</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO EN DIVISAS </t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>BOmba arrechisima</t>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Concreto tipo 2</t>
+  </si>
+  <si>
+    <t>alta</t>
   </si>
   <si>
     <t>25</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>bomba mas arrecha todaviaa</t>
-  </si>
-  <si>
-    <t>250</t>
   </si>
 </sst>
 </file>
@@ -574,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1004,8 +995,14 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3624,7 +3621,7 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="26" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="26"/>
@@ -3691,7 +3688,7 @@
         <v>-3</v>
       </c>
       <c r="B14" s="113" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="C14" s="113" t="s">
         <v>61</v>
@@ -3706,154 +3703,140 @@
         <v>64</v>
       </c>
       <c r="G14" s="116">
-        <v>10000</v>
+        <v>1250</v>
       </c>
       <c r="H14" s="118"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="119">
-        <v>-2</v>
-      </c>
-      <c r="B15" s="119" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="119" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="119" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="119" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="119" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" s="119">
-        <v>2500</v>
-      </c>
-      <c r="H15" s="120"/>
+      <c r="A15" s="119"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="120"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="121"/>
+      <c r="H15" s="122"/>
       <c r="I15" s="30"/>
     </row>
     <row r="16" ht="11.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="119"/>
-      <c r="B16" s="121"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="119"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="122"/>
+      <c r="B16" s="123"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="121"/>
+      <c r="H16" s="124"/>
       <c r="I16" s="30"/>
     </row>
     <row r="17" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="123"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="119"/>
-      <c r="H17" s="122"/>
+      <c r="A17" s="125"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="124"/>
       <c r="I17" s="30"/>
     </row>
     <row r="18" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="123"/>
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="119"/>
+      <c r="A18" s="125"/>
+      <c r="B18" s="123"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="120"/>
       <c r="F18" s="119"/>
       <c r="G18" s="119"/>
-      <c r="H18" s="124"/>
+      <c r="H18" s="126"/>
       <c r="I18" s="30"/>
     </row>
     <row r="19" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="123"/>
-      <c r="B19" s="121"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="125"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="124"/>
+      <c r="A19" s="125"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="127"/>
+      <c r="G19" s="127"/>
+      <c r="H19" s="126"/>
       <c r="I19" s="30"/>
     </row>
     <row r="20" ht="11.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="119"/>
-      <c r="B20" s="126"/>
-      <c r="C20" s="126"/>
+      <c r="B20" s="128"/>
+      <c r="C20" s="128"/>
       <c r="D20" s="119"/>
-      <c r="E20" s="126"/>
+      <c r="E20" s="128"/>
       <c r="F20" s="119"/>
       <c r="G20" s="119"/>
-      <c r="H20" s="127"/>
+      <c r="H20" s="129"/>
       <c r="I20" s="30"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="119"/>
-      <c r="B21" s="126"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="125"/>
-      <c r="G21" s="125"/>
-      <c r="H21" s="124"/>
+      <c r="B21" s="128"/>
+      <c r="C21" s="128"/>
+      <c r="D21" s="128"/>
+      <c r="E21" s="128"/>
+      <c r="F21" s="127"/>
+      <c r="G21" s="127"/>
+      <c r="H21" s="126"/>
       <c r="I21" s="30"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="119"/>
-      <c r="B22" s="126"/>
-      <c r="C22" s="126"/>
-      <c r="D22" s="126"/>
-      <c r="E22" s="126"/>
-      <c r="F22" s="125"/>
-      <c r="G22" s="125"/>
-      <c r="H22" s="124"/>
+      <c r="B22" s="128"/>
+      <c r="C22" s="128"/>
+      <c r="D22" s="128"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="127"/>
+      <c r="G22" s="127"/>
+      <c r="H22" s="126"/>
       <c r="I22" s="30"/>
     </row>
     <row r="23" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="119"/>
-      <c r="B23" s="128"/>
-      <c r="C23" s="128"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="128"/>
+      <c r="B23" s="130"/>
+      <c r="C23" s="130"/>
+      <c r="D23" s="130"/>
+      <c r="E23" s="130"/>
       <c r="F23" s="119"/>
       <c r="G23" s="119"/>
-      <c r="H23" s="129"/>
+      <c r="H23" s="131"/>
       <c r="I23" s="30"/>
     </row>
     <row r="24" ht="11.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="119"/>
-      <c r="B24" s="128"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="128"/>
-      <c r="G24" s="128"/>
-      <c r="H24" s="130"/>
+      <c r="B24" s="130"/>
+      <c r="C24" s="130"/>
+      <c r="D24" s="130"/>
+      <c r="E24" s="130"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="130"/>
+      <c r="H24" s="132"/>
       <c r="I24" s="30"/>
     </row>
     <row r="25" ht="8.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="128"/>
-      <c r="B25" s="128"/>
-      <c r="C25" s="128"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="128"/>
-      <c r="F25" s="128"/>
-      <c r="G25" s="128"/>
-      <c r="H25" s="130"/>
+      <c r="A25" s="130"/>
+      <c r="B25" s="130"/>
+      <c r="C25" s="130"/>
+      <c r="D25" s="130"/>
+      <c r="E25" s="130"/>
+      <c r="F25" s="130"/>
+      <c r="G25" s="130"/>
+      <c r="H25" s="132"/>
       <c r="I25" s="30"/>
     </row>
     <row r="26" ht="14.1" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="128"/>
-      <c r="B26" s="128"/>
-      <c r="C26" s="128"/>
-      <c r="D26" s="128"/>
-      <c r="E26" s="128"/>
-      <c r="F26" s="128"/>
-      <c r="G26" s="128"/>
-      <c r="H26" s="130"/>
+      <c r="A26" s="130"/>
+      <c r="B26" s="130"/>
+      <c r="C26" s="130"/>
+      <c r="D26" s="130"/>
+      <c r="E26" s="130"/>
+      <c r="F26" s="130"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="132"/>
       <c r="I26" s="30"/>
     </row>
     <row r="27" ht="14.1" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3862,31 +3845,31 @@
       <c r="C27" s="119"/>
       <c r="D27" s="119"/>
       <c r="E27" s="119"/>
-      <c r="F27" s="128"/>
-      <c r="G27" s="128"/>
-      <c r="H27" s="130"/>
+      <c r="F27" s="130"/>
+      <c r="G27" s="130"/>
+      <c r="H27" s="132"/>
       <c r="I27" s="30"/>
     </row>
     <row r="28" ht="14.1" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="119"/>
-      <c r="B28" s="119"/>
-      <c r="C28" s="119"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
+      <c r="A28" s="120"/>
+      <c r="B28" s="120"/>
+      <c r="C28" s="120"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="120"/>
       <c r="F28" s="119"/>
       <c r="G28" s="119"/>
-      <c r="H28" s="127"/>
+      <c r="H28" s="129"/>
       <c r="I28" s="30"/>
     </row>
     <row r="29" ht="14.1" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="131"/>
-      <c r="B29" s="131"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="131"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="131"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="132"/>
+      <c r="A29" s="133"/>
+      <c r="B29" s="133"/>
+      <c r="C29" s="133"/>
+      <c r="D29" s="133"/>
+      <c r="E29" s="133"/>
+      <c r="F29" s="133"/>
+      <c r="G29" s="133"/>
+      <c r="H29" s="134"/>
       <c r="I29" s="30"/>
     </row>
     <row r="30" ht="14.1" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3908,7 +3891,7 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="133" t="s">
+      <c r="H31" s="135" t="s">
         <v>35</v>
       </c>
       <c r="I31" s="30"/>
@@ -3921,11 +3904,11 @@
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="134">
-        <v>12500</v>
-      </c>
-      <c r="I32" s="134"/>
-      <c r="J32" s="133"/>
+      <c r="H32" s="136">
+        <v>1250</v>
+      </c>
+      <c r="I32" s="136"/>
+      <c r="J32" s="135"/>
     </row>
     <row r="33" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F33" s="4"/>
